--- a/output/yearly_total_coral_cover_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_42_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.268542161369512</v>
+        <v>1.255475099425987</v>
       </c>
       <c r="C3" t="n">
-        <v>4.673292732618631</v>
+        <v>4.657859658707872</v>
       </c>
       <c r="D3" t="n">
-        <v>6.032157421876839</v>
+        <v>6.050251032066106</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97399231586498</v>
+        <v>11.96358579019996</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.426628818891285</v>
+        <v>1.38478851905292</v>
       </c>
       <c r="C4" t="n">
-        <v>5.245381785476472</v>
+        <v>5.209390454289999</v>
       </c>
       <c r="D4" t="n">
-        <v>6.304543769289509</v>
+        <v>6.356930037060665</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97655437365727</v>
+        <v>12.95110901040358</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.634295781901068</v>
+        <v>1.558982969794712</v>
       </c>
       <c r="C5" t="n">
-        <v>5.986526028851978</v>
+        <v>5.944604469179136</v>
       </c>
       <c r="D5" t="n">
-        <v>6.564816690412487</v>
+        <v>6.671416302826649</v>
       </c>
       <c r="E5" t="n">
-        <v>14.18563850116553</v>
+        <v>14.1750037418005</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.862400299026972</v>
+        <v>1.760150940224093</v>
       </c>
       <c r="C6" t="n">
-        <v>6.908737016804534</v>
+        <v>6.834584548476475</v>
       </c>
       <c r="D6" t="n">
-        <v>6.818207216472882</v>
+        <v>7.124986109613792</v>
       </c>
       <c r="E6" t="n">
-        <v>15.58934453230439</v>
+        <v>15.71972159831436</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.119386140374374</v>
+        <v>1.986137226145374</v>
       </c>
       <c r="C7" t="n">
-        <v>7.977093375594738</v>
+        <v>7.916101437256577</v>
       </c>
       <c r="D7" t="n">
-        <v>7.164234820709602</v>
+        <v>7.633082760731529</v>
       </c>
       <c r="E7" t="n">
-        <v>17.26071433667871</v>
+        <v>17.53532142413348</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.319173366981492</v>
+        <v>1.202112751494296</v>
       </c>
       <c r="C8" t="n">
-        <v>5.581628494659862</v>
+        <v>5.635045234595736</v>
       </c>
       <c r="D8" t="n">
-        <v>5.321491614651936</v>
+        <v>5.890996730572594</v>
       </c>
       <c r="E8" t="n">
-        <v>12.22229347629329</v>
+        <v>12.72815471666262</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.66202077561856</v>
+        <v>1.481179228932202</v>
       </c>
       <c r="C9" t="n">
-        <v>6.814413737470555</v>
+        <v>7.052122287958493</v>
       </c>
       <c r="D9" t="n">
-        <v>5.749080534008461</v>
+        <v>6.425656612824859</v>
       </c>
       <c r="E9" t="n">
-        <v>14.22551504709758</v>
+        <v>14.95895812971555</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.018680808223269</v>
+        <v>1.76521476480086</v>
       </c>
       <c r="C10" t="n">
-        <v>8.135567438941246</v>
+        <v>8.651976790124166</v>
       </c>
       <c r="D10" t="n">
-        <v>6.117937497530826</v>
+        <v>7.002972162565551</v>
       </c>
       <c r="E10" t="n">
-        <v>16.27218574469534</v>
+        <v>17.42016371749058</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.382876970087129</v>
+        <v>2.047045826710639</v>
       </c>
       <c r="C11" t="n">
-        <v>9.546679920611181</v>
+        <v>10.35283811007871</v>
       </c>
       <c r="D11" t="n">
-        <v>6.467605190715706</v>
+        <v>7.647425605586569</v>
       </c>
       <c r="E11" t="n">
-        <v>18.39716208141402</v>
+        <v>20.04730954237592</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.760533254885229</v>
+        <v>2.31268244098114</v>
       </c>
       <c r="C12" t="n">
-        <v>11.00146217127637</v>
+        <v>12.05839913921566</v>
       </c>
       <c r="D12" t="n">
-        <v>6.858562449124443</v>
+        <v>8.17874511407973</v>
       </c>
       <c r="E12" t="n">
-        <v>20.62055787528604</v>
+        <v>22.54982669427653</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.120825837996358</v>
+        <v>2.557011882335623</v>
       </c>
       <c r="C13" t="n">
-        <v>12.54510566236882</v>
+        <v>13.77369681086823</v>
       </c>
       <c r="D13" t="n">
-        <v>7.259117500456487</v>
+        <v>8.679868196744561</v>
       </c>
       <c r="E13" t="n">
-        <v>22.92504900082167</v>
+        <v>25.01057688994841</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.806121251502857</v>
+        <v>1.474486877008284</v>
       </c>
       <c r="C14" t="n">
-        <v>8.900465781839328</v>
+        <v>9.51145646557733</v>
       </c>
       <c r="D14" t="n">
-        <v>5.521123286712085</v>
+        <v>6.586525712837767</v>
       </c>
       <c r="E14" t="n">
-        <v>16.22771032005427</v>
+        <v>17.57246905542338</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.856023487309723</v>
+        <v>1.483234249053123</v>
       </c>
       <c r="C15" t="n">
-        <v>9.481336446011039</v>
+        <v>10.26024525708342</v>
       </c>
       <c r="D15" t="n">
-        <v>5.459597158086938</v>
+        <v>6.637900570201</v>
       </c>
       <c r="E15" t="n">
-        <v>16.7969570914077</v>
+        <v>18.38138007633754</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.156909523707285</v>
+        <v>1.694506355007037</v>
       </c>
       <c r="C16" t="n">
-        <v>11.1488251041972</v>
+        <v>12.03253548269793</v>
       </c>
       <c r="D16" t="n">
-        <v>5.791496604461656</v>
+        <v>7.127164356089443</v>
       </c>
       <c r="E16" t="n">
-        <v>19.09723123236614</v>
+        <v>20.85420619379441</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.731488791026015</v>
+        <v>1.341685865054819</v>
       </c>
       <c r="C17" t="n">
-        <v>10.18952996994652</v>
+        <v>10.98344970341683</v>
       </c>
       <c r="D17" t="n">
-        <v>5.314161053179814</v>
+        <v>6.64641232279682</v>
       </c>
       <c r="E17" t="n">
-        <v>17.23517981415235</v>
+        <v>18.97154789126847</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.99320309402413</v>
+        <v>1.505186127720082</v>
       </c>
       <c r="C18" t="n">
-        <v>11.91090675961879</v>
+        <v>12.7272496106541</v>
       </c>
       <c r="D18" t="n">
-        <v>5.652618574218902</v>
+        <v>7.078450035004715</v>
       </c>
       <c r="E18" t="n">
-        <v>19.55672842786182</v>
+        <v>21.3108857733789</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.016666864155628</v>
+        <v>1.490243927661446</v>
       </c>
       <c r="C19" t="n">
-        <v>12.74869098051485</v>
+        <v>13.51215690019942</v>
       </c>
       <c r="D19" t="n">
-        <v>5.694077779769246</v>
+        <v>7.18762037971696</v>
       </c>
       <c r="E19" t="n">
-        <v>20.45943562443972</v>
+        <v>22.19002120757783</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.260238469579262</v>
+        <v>1.643367117092821</v>
       </c>
       <c r="C20" t="n">
-        <v>14.72653954044456</v>
+        <v>15.44026030395495</v>
       </c>
       <c r="D20" t="n">
-        <v>6.023601396699687</v>
+        <v>7.692484136625882</v>
       </c>
       <c r="E20" t="n">
-        <v>23.01037940672351</v>
+        <v>24.77611155767365</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.352701074296468</v>
+        <v>0.9684253879001812</v>
       </c>
       <c r="C21" t="n">
-        <v>10.96094804603549</v>
+        <v>11.25788745666198</v>
       </c>
       <c r="D21" t="n">
-        <v>4.972974273522921</v>
+        <v>6.435513280970522</v>
       </c>
       <c r="E21" t="n">
-        <v>17.28662339385488</v>
+        <v>18.66182612553268</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_42_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255475099425987</v>
+        <v>1.252844015578606</v>
       </c>
       <c r="C3" t="n">
-        <v>4.657859658707872</v>
+        <v>4.581018265896473</v>
       </c>
       <c r="D3" t="n">
-        <v>6.050251032066106</v>
+        <v>6.145892893413832</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96358579019996</v>
+        <v>11.97975517488891</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.38478851905292</v>
+        <v>1.383352390662794</v>
       </c>
       <c r="C4" t="n">
-        <v>5.209390454289999</v>
+        <v>4.99970406003334</v>
       </c>
       <c r="D4" t="n">
-        <v>6.356930037060665</v>
+        <v>6.426869416835688</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95110901040358</v>
+        <v>12.80992586753182</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.558982969794712</v>
+        <v>1.566939162439866</v>
       </c>
       <c r="C5" t="n">
-        <v>5.944604469179136</v>
+        <v>5.499327413589558</v>
       </c>
       <c r="D5" t="n">
-        <v>6.671416302826649</v>
+        <v>6.765413811440679</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1750037418005</v>
+        <v>13.8316803874701</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.760150940224093</v>
+        <v>1.773104964978088</v>
       </c>
       <c r="C6" t="n">
-        <v>6.834584548476475</v>
+        <v>6.099529085637349</v>
       </c>
       <c r="D6" t="n">
-        <v>7.124986109613792</v>
+        <v>7.235568904223091</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71972159831436</v>
+        <v>15.10820295483853</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.986137226145374</v>
+        <v>2.003796354492791</v>
       </c>
       <c r="C7" t="n">
-        <v>7.916101437256577</v>
+        <v>6.85258767580834</v>
       </c>
       <c r="D7" t="n">
-        <v>7.633082760731529</v>
+        <v>7.697141905468396</v>
       </c>
       <c r="E7" t="n">
-        <v>17.53532142413348</v>
+        <v>16.55352593576953</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.202112751494296</v>
+        <v>1.234209039110629</v>
       </c>
       <c r="C8" t="n">
-        <v>5.635045234595736</v>
+        <v>4.587410694153029</v>
       </c>
       <c r="D8" t="n">
-        <v>5.890996730572594</v>
+        <v>5.936035640387694</v>
       </c>
       <c r="E8" t="n">
-        <v>12.72815471666262</v>
+        <v>11.75765537365135</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.481179228932202</v>
+        <v>1.548817892884351</v>
       </c>
       <c r="C9" t="n">
-        <v>7.052122287958493</v>
+        <v>5.647406099798952</v>
       </c>
       <c r="D9" t="n">
-        <v>6.425656612824859</v>
+        <v>6.477662244952935</v>
       </c>
       <c r="E9" t="n">
-        <v>14.95895812971555</v>
+        <v>13.67388623763624</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.76521476480086</v>
+        <v>1.892766760767811</v>
       </c>
       <c r="C10" t="n">
-        <v>8.651976790124166</v>
+        <v>6.937542435578715</v>
       </c>
       <c r="D10" t="n">
-        <v>7.002972162565551</v>
+        <v>7.149436668386933</v>
       </c>
       <c r="E10" t="n">
-        <v>17.42016371749058</v>
+        <v>15.97974586473346</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.047045826710639</v>
+        <v>2.235314215964581</v>
       </c>
       <c r="C11" t="n">
-        <v>10.35283811007871</v>
+        <v>8.330945550369634</v>
       </c>
       <c r="D11" t="n">
-        <v>7.647425605586569</v>
+        <v>7.770134400410059</v>
       </c>
       <c r="E11" t="n">
-        <v>20.04730954237592</v>
+        <v>18.33639416674427</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.31268244098114</v>
+        <v>2.57897166049673</v>
       </c>
       <c r="C12" t="n">
-        <v>12.05839913921566</v>
+        <v>9.802983020167558</v>
       </c>
       <c r="D12" t="n">
-        <v>8.17874511407973</v>
+        <v>8.395497667992334</v>
       </c>
       <c r="E12" t="n">
-        <v>22.54982669427653</v>
+        <v>20.77745234865662</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.557011882335623</v>
+        <v>2.924677184104736</v>
       </c>
       <c r="C13" t="n">
-        <v>13.77369681086823</v>
+        <v>11.34834432575247</v>
       </c>
       <c r="D13" t="n">
-        <v>8.679868196744561</v>
+        <v>8.960823494258541</v>
       </c>
       <c r="E13" t="n">
-        <v>25.01057688994841</v>
+        <v>23.23384500411574</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.474486877008284</v>
+        <v>1.690412467080328</v>
       </c>
       <c r="C14" t="n">
-        <v>9.51145646557733</v>
+        <v>7.908429361652011</v>
       </c>
       <c r="D14" t="n">
-        <v>6.586525712837767</v>
+        <v>6.7907979576604</v>
       </c>
       <c r="E14" t="n">
-        <v>17.57246905542338</v>
+        <v>16.38963978639274</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.483234249053123</v>
+        <v>1.741276815637355</v>
       </c>
       <c r="C15" t="n">
-        <v>10.26024525708342</v>
+        <v>8.621855600851125</v>
       </c>
       <c r="D15" t="n">
-        <v>6.637900570201</v>
+        <v>6.891201295373722</v>
       </c>
       <c r="E15" t="n">
-        <v>18.38138007633754</v>
+        <v>17.2543337118622</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.694506355007037</v>
+        <v>2.040150269241212</v>
       </c>
       <c r="C16" t="n">
-        <v>12.03253548269793</v>
+        <v>10.21664584153782</v>
       </c>
       <c r="D16" t="n">
-        <v>7.127164356089443</v>
+        <v>7.494455807202258</v>
       </c>
       <c r="E16" t="n">
-        <v>20.85420619379441</v>
+        <v>19.75125191798129</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.341685865054819</v>
+        <v>1.651584345377367</v>
       </c>
       <c r="C17" t="n">
-        <v>10.98344970341683</v>
+        <v>9.491487717272951</v>
       </c>
       <c r="D17" t="n">
-        <v>6.64641232279682</v>
+        <v>7.016040333445746</v>
       </c>
       <c r="E17" t="n">
-        <v>18.97154789126847</v>
+        <v>18.15911239609606</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.505186127720082</v>
+        <v>1.894105480757456</v>
       </c>
       <c r="C18" t="n">
-        <v>12.7272496106541</v>
+        <v>11.01830174691759</v>
       </c>
       <c r="D18" t="n">
-        <v>7.078450035004715</v>
+        <v>7.584825683378178</v>
       </c>
       <c r="E18" t="n">
-        <v>21.3108857733789</v>
+        <v>20.49723291105322</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.490243927661446</v>
+        <v>1.907054732976472</v>
       </c>
       <c r="C19" t="n">
-        <v>13.51215690019942</v>
+        <v>11.73026518203738</v>
       </c>
       <c r="D19" t="n">
-        <v>7.18762037971696</v>
+        <v>7.73662351340882</v>
       </c>
       <c r="E19" t="n">
-        <v>22.19002120757783</v>
+        <v>21.37394342842267</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.643367117092821</v>
+        <v>2.130942296929957</v>
       </c>
       <c r="C20" t="n">
-        <v>15.44026030395495</v>
+        <v>13.46454213654345</v>
       </c>
       <c r="D20" t="n">
-        <v>7.692484136625882</v>
+        <v>8.379462092672588</v>
       </c>
       <c r="E20" t="n">
-        <v>24.77611155767365</v>
+        <v>23.974946526146</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9684253879001812</v>
+        <v>1.269350694205914</v>
       </c>
       <c r="C21" t="n">
-        <v>11.25788745666198</v>
+        <v>9.840420486316352</v>
       </c>
       <c r="D21" t="n">
-        <v>6.435513280970522</v>
+        <v>7.059099787754011</v>
       </c>
       <c r="E21" t="n">
-        <v>18.66182612553268</v>
+        <v>18.16887096827628</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_42_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252844015578606</v>
+        <v>2.612597059994014</v>
       </c>
       <c r="C3" t="n">
-        <v>4.581018265896473</v>
+        <v>7.671746794468696</v>
       </c>
       <c r="D3" t="n">
-        <v>6.145892893413832</v>
+        <v>8.198415803589855</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97975517488891</v>
+        <v>18.48275965805257</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.383352390662794</v>
+        <v>1.111271466167912</v>
       </c>
       <c r="C4" t="n">
-        <v>4.99970406003334</v>
+        <v>4.4230083844096</v>
       </c>
       <c r="D4" t="n">
-        <v>6.426869416835688</v>
+        <v>5.823295531755532</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80992586753182</v>
+        <v>11.35757538233304</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.566939162439866</v>
+        <v>1.232971751374444</v>
       </c>
       <c r="C5" t="n">
-        <v>5.499327413589558</v>
+        <v>4.979764710913562</v>
       </c>
       <c r="D5" t="n">
-        <v>6.765413811440679</v>
+        <v>6.146479216222451</v>
       </c>
       <c r="E5" t="n">
-        <v>13.8316803874701</v>
+        <v>12.35921567851046</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.773104964978088</v>
+        <v>1.37074140158696</v>
       </c>
       <c r="C6" t="n">
-        <v>6.099529085637349</v>
+        <v>5.668894151688536</v>
       </c>
       <c r="D6" t="n">
-        <v>7.235568904223091</v>
+        <v>6.471783250651659</v>
       </c>
       <c r="E6" t="n">
-        <v>15.10820295483853</v>
+        <v>13.51141880392715</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.003796354492791</v>
+        <v>1.518861312627414</v>
       </c>
       <c r="C7" t="n">
-        <v>6.85258767580834</v>
+        <v>6.511659259292494</v>
       </c>
       <c r="D7" t="n">
-        <v>7.697141905468396</v>
+        <v>6.843102257063008</v>
       </c>
       <c r="E7" t="n">
-        <v>16.55352593576953</v>
+        <v>14.87362282898292</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.234209039110629</v>
+        <v>1.68963103688546</v>
       </c>
       <c r="C8" t="n">
-        <v>4.587410694153029</v>
+        <v>7.48357105020798</v>
       </c>
       <c r="D8" t="n">
-        <v>5.936035640387694</v>
+        <v>7.268870811712558</v>
       </c>
       <c r="E8" t="n">
-        <v>11.75765537365135</v>
+        <v>16.442072898806</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.548817892884351</v>
+        <v>1.861808276418157</v>
       </c>
       <c r="C9" t="n">
-        <v>5.647406099798952</v>
+        <v>8.64202672854841</v>
       </c>
       <c r="D9" t="n">
-        <v>6.477662244952935</v>
+        <v>7.768717501612197</v>
       </c>
       <c r="E9" t="n">
-        <v>13.67388623763624</v>
+        <v>18.27255250657877</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.892766760767811</v>
+        <v>1.154790554597353</v>
       </c>
       <c r="C10" t="n">
-        <v>6.937542435578715</v>
+        <v>6.507377212921387</v>
       </c>
       <c r="D10" t="n">
-        <v>7.149436668386933</v>
+        <v>6.122856089599039</v>
       </c>
       <c r="E10" t="n">
-        <v>15.97974586473346</v>
+        <v>13.78502385711778</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.235314215964581</v>
+        <v>1.105339922734441</v>
       </c>
       <c r="C11" t="n">
-        <v>8.330945550369634</v>
+        <v>6.906418384789547</v>
       </c>
       <c r="D11" t="n">
-        <v>7.770134400410059</v>
+        <v>6.028284333248945</v>
       </c>
       <c r="E11" t="n">
-        <v>18.33639416674427</v>
+        <v>14.04004264077293</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.57897166049673</v>
+        <v>1.212527137084108</v>
       </c>
       <c r="C12" t="n">
-        <v>9.802983020167558</v>
+        <v>8.235822586064238</v>
       </c>
       <c r="D12" t="n">
-        <v>8.395497667992334</v>
+        <v>6.457200087757334</v>
       </c>
       <c r="E12" t="n">
-        <v>20.77745234865662</v>
+        <v>15.90554981090568</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.924677184104736</v>
+        <v>0.9651070806598269</v>
       </c>
       <c r="C13" t="n">
-        <v>11.34834432575247</v>
+        <v>7.954178804669914</v>
       </c>
       <c r="D13" t="n">
-        <v>8.960823494258541</v>
+        <v>5.94385403068372</v>
       </c>
       <c r="E13" t="n">
-        <v>23.23384500411574</v>
+        <v>14.86313991601346</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.690412467080328</v>
+        <v>1.053876708077824</v>
       </c>
       <c r="C14" t="n">
-        <v>7.908429361652011</v>
+        <v>9.405869499985586</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7907979576604</v>
+        <v>6.343327171541746</v>
       </c>
       <c r="E14" t="n">
-        <v>16.38963978639274</v>
+        <v>16.80307337960516</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.741276815637355</v>
+        <v>1.030196953451391</v>
       </c>
       <c r="C15" t="n">
-        <v>8.621855600851125</v>
+        <v>10.25864500832549</v>
       </c>
       <c r="D15" t="n">
-        <v>6.891201295373722</v>
+        <v>6.429573707359828</v>
       </c>
       <c r="E15" t="n">
-        <v>17.2543337118622</v>
+        <v>17.71841566913671</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.040150269241212</v>
+        <v>1.131621308777129</v>
       </c>
       <c r="C16" t="n">
-        <v>10.21664584153782</v>
+        <v>12.10605856826897</v>
       </c>
       <c r="D16" t="n">
-        <v>7.494455807202258</v>
+        <v>6.873421844449811</v>
       </c>
       <c r="E16" t="n">
-        <v>19.75125191798129</v>
+        <v>20.11110172149591</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.651584345377367</v>
+        <v>0.6769641294633881</v>
       </c>
       <c r="C17" t="n">
-        <v>9.491487717272951</v>
+        <v>9.21487048412437</v>
       </c>
       <c r="D17" t="n">
-        <v>7.016040333445746</v>
+        <v>5.733092433536013</v>
       </c>
       <c r="E17" t="n">
-        <v>18.15911239609606</v>
+        <v>15.62492704712377</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.894105480757456</v>
+        <v>0.5320483508395164</v>
       </c>
       <c r="C18" t="n">
-        <v>11.01830174691759</v>
+        <v>8.410180978338472</v>
       </c>
       <c r="D18" t="n">
-        <v>7.584825683378178</v>
+        <v>5.250965953457447</v>
       </c>
       <c r="E18" t="n">
-        <v>20.49723291105322</v>
+        <v>14.19319528263544</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.907054732976472</v>
+        <v>0.6199049528925635</v>
       </c>
       <c r="C19" t="n">
-        <v>11.73026518203738</v>
+        <v>10.50445499851481</v>
       </c>
       <c r="D19" t="n">
-        <v>7.73662351340882</v>
+        <v>5.79799577426377</v>
       </c>
       <c r="E19" t="n">
-        <v>21.37394342842267</v>
+        <v>16.92235572567114</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.130942296929957</v>
+        <v>0.7039229214220056</v>
       </c>
       <c r="C20" t="n">
-        <v>13.46454213654345</v>
+        <v>12.68851966372156</v>
       </c>
       <c r="D20" t="n">
-        <v>8.379462092672588</v>
+        <v>6.340205213842241</v>
       </c>
       <c r="E20" t="n">
-        <v>23.974946526146</v>
+        <v>19.73264779898581</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.269350694205914</v>
+        <v>0.7774558244700918</v>
       </c>
       <c r="C21" t="n">
-        <v>9.840420486316352</v>
+        <v>14.86553538041182</v>
       </c>
       <c r="D21" t="n">
-        <v>7.059099787754011</v>
+        <v>6.850949639499603</v>
       </c>
       <c r="E21" t="n">
-        <v>18.16887096827628</v>
+        <v>22.49394084438152</v>
       </c>
     </row>
   </sheetData>
